--- a/enhancements/compIntRequirements.xlsx
+++ b/enhancements/compIntRequirements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bsubbarao/MYDATA/CompIntCalculator/enhancements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8FF3B7B4-8504-0247-9D88-16541249DECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07808DDF-230C-9D4B-857A-6BAAF6B00637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5800" yWindow="2120" windowWidth="27640" windowHeight="16680" xr2:uid="{653E4233-7205-4545-9EB2-882F0BD02EB4}"/>
   </bookViews>
@@ -496,5 +496,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>